--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,16 +161,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,20 +787,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="F4" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -805,40 +808,38 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>6.8</v>
+      <c r="L4" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>86.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q4" s="12" t="n">
+      <c r="R4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S4" s="12" t="n">
+      <c r="S4" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="T4" s="12" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U4" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="14" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr"/>
       <c r="W4" s="12" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -857,20 +858,20 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="F5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>5.4</v>
@@ -878,51 +879,53 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.4</v>
+      <c r="K5" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="12" t="n">
+      <c r="R5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="12" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="12" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="U5" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="T5" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="V5" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="W5" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="X5" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>13.6</v>
+      <c r="X5" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>9.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -937,17 +940,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
-        <v>2.8</v>
+      <c r="C6" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>28.6</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="F6" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -959,53 +964,53 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M6" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="12" t="n">
+      <c r="M6" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="O6" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="P6" s="12" t="n">
+      <c r="O6" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S6" s="12" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T6" s="12" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="U6" s="12" t="n">
-        <v>13</v>
+      <c r="S6" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="V6" s="12" t="n">
         <v>24.6</v>
       </c>
       <c r="W6" s="12" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="X6" s="12" t="n">
-        <v>20.7</v>
+        <v>23.4</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>67</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>10.2</v>
+        <v>7.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1020,7 +1025,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D7" s="12" t="n">
         <v>30.4</v>
       </c>
@@ -1040,55 +1047,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>7.4</v>
+      <c r="L7" s="9" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R7" s="12" t="n">
+      <c r="Q7" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="S7" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="T7" s="12" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="U7" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>0.4</v>
+      <c r="S7" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <v>25.8</v>
       </c>
       <c r="W7" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>14.9</v>
+      <c r="X7" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>10.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1104,31 +1111,35 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
-        <v>22.9</v>
+      <c r="D8" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>53.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="14" t="inlineStr"/>
+      <c r="L8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="M8" s="3" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1136,34 +1147,38 @@
       <c r="O8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="12" t="n">
+      <c r="P8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S8" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="T8" s="12" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="U8" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>25.8</v>
+      <c r="S8" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>26.2</v>
       </c>
       <c r="W8" s="12" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="n">
-        <v>14.8</v>
+        <v>19.8</v>
+      </c>
+      <c r="X8" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Y8" s="12" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="Z8" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1178,27 +1193,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>142.8</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="10" t="n">
+        <v>711.7</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -1208,25 +1225,25 @@
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>423.5</v>
+        <v>201122.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>192.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>186</v>
+        <v>1196</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>102.6</v>
+        <v>182.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>263.1</v>
+        <v>9255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
@@ -1235,16 +1252,16 @@
         <v>127.2</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>97.40000000000001</v>
+        <v>971.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>229.9</v>
+        <v>294.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1270,7 +1287,7 @@
         <v>23.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>16.5</v>
@@ -1279,10 +1296,10 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>51.1</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>18.8</v>
@@ -1299,35 +1316,35 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="S10" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="T10" s="12" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="U10" s="12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="V10" s="10" t="n">
+      <c r="S10" s="3" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V10" s="12" t="n">
         <v>25.4</v>
       </c>
       <c r="W10" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>13.9</v>
+      <c r="X10" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1343,23 +1360,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="D11" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.2</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.6</v>
+        <v>15.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1367,7 +1384,7 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M11" s="8" t="n">
@@ -1377,29 +1394,41 @@
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="R11" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>18.4</v>
+      <c r="S11" s="8" t="n">
+        <v>166.6</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="12" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>13.4</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W11" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>13.4</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1413,7 +1442,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D12" s="12" t="n">
         <v>28.2</v>
       </c>
@@ -1438,10 +1469,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1451,7 +1482,7 @@
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>2.8</v>
@@ -1463,23 +1494,25 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="12" t="n">
-        <v>25.6</v>
+        <v>425.4</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>45.4</v>
       </c>
       <c r="W12" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X12" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y12" s="12" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="Z12" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>19.9</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1541,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1517,9 +1550,9 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1529,10 +1562,10 @@
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>23.5</v>
+        <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1541,28 +1574,28 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>57.1</v>
+        <v>257.1</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V13" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="X13" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y13" s="12" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="Z13" s="12" t="n">
-        <v>9.699999999999999</v>
+      <c r="X13" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>58</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1582,35 +1615,37 @@
         <v>27.4</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+        <v>23.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>47.8</v>
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>714.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1619,31 +1654,31 @@
         <v>26.8</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>51.5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V14" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="V14" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="X14" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y14" s="12" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="Z14" s="12" t="n">
-        <v>7.6</v>
+      <c r="X14" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1663,12 +1698,12 @@
         <v>28.8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1680,21 +1715,23 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N15" s="3" t="n">
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N15" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="O15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>13.4</v>
+      <c r="O15" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>3.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1711,20 +1748,20 @@
       <c r="U15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="12" t="n">
-        <v>25.4</v>
+      <c r="V15" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="W15" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Y15" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X15" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="Z15" s="12" t="n">
-        <v>10.8</v>
+      <c r="Z15" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1739,50 +1776,56 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
-        <v>1038.8</v>
-      </c>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
-        <v>1113.9</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="C16" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3019.1</v>
+        <v>288.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>92</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>914.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
+        <v>709.1</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="Q16" s="10" t="n">
-        <v>838.2</v>
-      </c>
-      <c r="R16" s="10" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>266.2</v>
@@ -1791,9 +1834,9 @@
         <v>86.2</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="W16" s="10" t="n">
+        <v>1943.1</v>
+      </c>
+      <c r="W16" s="12" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1803,7 +1846,7 @@
         <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1819,20 +1862,20 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="10" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E17" s="3" t="n">
+      <c r="D17" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="12" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>0.1</v>
+      <c r="G17" s="12" t="n">
+        <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1840,51 +1883,53 @@
       <c r="J17" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>8.4</v>
+      <c r="N17" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="P17" s="12" t="n">
+        <v>2.4</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="12" t="n">
-        <v>20.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>11.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y17" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z17" s="12" t="n">
-        <v>9</v>
+      <c r="W17" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1899,70 +1944,78 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="3" t="n">
-        <v>8.4</v>
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>38.4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.1</v>
+        <v>13.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>13.6</v>
+        <v>456.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>13.6</v>
+        <v>126.1</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>49.6</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>17.8</v>
+      <c r="N18" s="8" t="n">
+        <v>68.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>78.8</v>
+        <v>810.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R18" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="Q18" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>904.7</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>811.1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="T18" s="12" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="U18" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="W18" s="12" t="n">
-        <v>20.2</v>
+      <c r="W18" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
+        <v>457.1</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>91.40000000000001</v>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1977,10 +2030,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>17.8</v>
@@ -1992,7 +2045,7 @@
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -2001,7 +2054,7 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
@@ -2009,42 +2062,44 @@
       <c r="M19" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>18.7</v>
+      <c r="N19" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="R19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="S19" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="T19" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
+      <c r="T19" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U19" s="12" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="12" t="n">
+      <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2059,7 +2114,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D20" s="12" t="n">
         <v>30.6</v>
       </c>
@@ -2069,12 +2126,14 @@
       <c r="F20" s="12" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="G20" s="12" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H20" s="8" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
@@ -2107,25 +2166,25 @@
         <v>20.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2141,14 +2200,14 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>2.2</v>
+      <c r="D21" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>22.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2160,19 +2219,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>19</v>
+      <c r="N21" s="12" t="n">
+        <v>19.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2180,7 +2239,9 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="14" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2188,22 +2249,22 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>256</v>
+        <v>56.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="12" t="n">
+      <c r="W21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2221,17 +2282,19 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="n">
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2247,13 +2310,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2261,35 +2324,35 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T22" s="3" t="n">
+      <c r="R22" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S22" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T22" s="12" t="n">
         <v>68.3</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="12" t="n">
+      <c r="W22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>155.1</v>
+        <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.7</v>
+        <v>254.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2304,9 +2367,11 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D23" s="10" t="n">
-        <v>19.6</v>
+        <v>1945.6</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>89.40000000000001</v>
@@ -2315,64 +2380,64 @@
         <v>117.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.2</v>
+        <v>36.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>529.5</v>
+        <v>311.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.9</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>1426.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>44</v>
+        <v>140.4</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>103.9</v>
+        <v>103.4</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>100.4</v>
+        <v>1108.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8267.799999999999</v>
+        <v>267.8</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>123.5</v>
+        <v>1123.5</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>25.6</v>
+        <v>935.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94.8</v>
+        <v>26</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>205.4</v>
+        <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.8</v>
+        <v>652.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2401,7 +2466,7 @@
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2409,26 +2474,26 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L24" s="12" t="n">
+      <c r="K24" s="8" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="L24" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="O24" s="12" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P24" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="10" t="n">
-        <v>28.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>20.7</v>
@@ -2437,25 +2502,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W24" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="W24" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.6</v>
+        <v>171.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2470,21 +2535,23 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.6</v>
+      <c r="C25" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2496,40 +2563,48 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="14" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>91.40000000000001</v>
+      </c>
       <c r="R25" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>662.3</v>
+        <v>405.5</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>12.8</v>
+        <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2543,29 +2618,27 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>16</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2576,12 +2649,14 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2593,25 +2668,25 @@
         <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>12.2</v>
+        <v>52.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="W26" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>18.6</v>
+        <v>38.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>19.8</v>
+        <v>112.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2626,74 +2701,76 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>12.8</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>68.7</v>
+        <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>4.1</v>
+      <c r="Q27" s="12" t="n">
+        <v>27.4</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S27" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S27" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.8</v>
+      <c r="T27" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U27" s="12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="V27" s="12" t="n">
+        <v>24.9</v>
       </c>
       <c r="W27" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X27" s="12" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Y27" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z27" s="12" t="n">
+        <v>11.4</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2707,44 +2784,46 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="C28" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G28" s="12" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3" t="n">
+      <c r="M28" s="12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N28" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="P28" s="12" t="n">
         <v>3.4</v>
       </c>
       <c r="Q28" s="12" t="n">
@@ -2757,22 +2836,26 @@
         <v>20.7</v>
       </c>
       <c r="T28" s="12" t="n">
-        <v>56.7</v>
+        <v>56.9</v>
       </c>
       <c r="U28" s="12" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>19.8</v>
+        <v>29.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2786,69 +2869,71 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D29" s="12" t="n">
         <v>26.8</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G29" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="O29" s="12" t="n">
+      <c r="M29" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O29" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P29" s="12" t="n">
+      <c r="P29" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="12" t="n">
         <v>25.6</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>152.5</v>
+        <v>17.2</v>
+      </c>
+      <c r="S29" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T29" s="12" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="U29" s="12" t="n">
+        <v>13.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W29" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>19.8</v>
+      <c r="X29" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2869,44 +2954,42 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1334.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="12" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="E30" s="12" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>48.4</v>
+      <c r="F30" s="12" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>32.8</v>
+        <v>39.8</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>90.40000000000001</v>
+        <v>308.4</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>91.40000000000001</v>
+        <v>9434.799999999999</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>185.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>904.6</v>
+        <v>9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43464.4</v>
+        <v>428</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>15.2</v>
@@ -2918,28 +3001,28 @@
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>102.2</v>
+        <v>41.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>298.9</v>
+        <v>448.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V30" s="10" t="n">
         <v>118.2</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>99.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>418.1</v>
+        <v>44.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>3136.2</v>
+        <v>316.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.6</v>
+        <v>47.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2954,9 +3037,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="12" t="n">
         <v>26.6</v>
       </c>
@@ -2966,11 +3047,11 @@
       <c r="F31" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>9.9</v>
+      <c r="G31" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26.1</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -2978,29 +3059,27 @@
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="P31" s="12" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q31" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>20.4</v>
+      <c r="R31" s="10" t="n">
+        <v>10.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3009,22 +3088,22 @@
         <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="12" t="n">
+      <c r="W31" s="10" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>475.1</v>
+        <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3039,73 +3118,71 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E32" s="14" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
+      <c r="C32" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>19.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>15.2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R32" s="12" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X32" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y32" s="12" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="Z32" s="12" t="n">
-        <v>5.7</v>
+        <v>96.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="V32" s="12" t="inlineStr"/>
+      <c r="W32" s="9" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>4412.8</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3121,16 +3198,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="D33" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3140,7 +3217,7 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3148,47 +3225,47 @@
       <c r="L33" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O33" s="3" t="n">
+      <c r="M33" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O33" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="P33" s="12" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q33" s="12" t="n">
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R33" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S33" s="12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T33" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="U33" s="12" t="n">
-        <v>15.3</v>
+      <c r="R33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="V33" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="12" t="n">
+      <c r="W33" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X33" s="12" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="Y33" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z33" s="12" t="n">
-        <v>4.7</v>
+      <c r="X33" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3204,17 +3281,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>1.7</v>
+      <c r="D34" s="9" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>16.6</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17</v>
@@ -3226,9 +3303,9 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3238,40 +3315,40 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="12" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="S34" s="12" t="n">
+      <c r="R34" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S34" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="T34" s="12" t="n">
+      <c r="T34" s="3" t="n">
         <v>57.2</v>
       </c>
-      <c r="U34" s="12" t="n">
-        <v>16.4</v>
+      <c r="U34" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="V34" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="12" t="n">
+      <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X34" s="12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Y34" s="12" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="Z34" s="12" t="n">
-        <v>7.6</v>
+      <c r="X34" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3286,20 +3363,18 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>10.8</v>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
@@ -3313,50 +3388,50 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>17.6</v>
+      <c r="L35" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q35" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R35" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S35" s="12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="T35" s="12" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U35" s="12" t="n">
+      <c r="T35" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="V35" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="12" t="n">
+      <c r="W35" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="X35" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y35" s="12" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z35" s="12" t="n">
-        <v>2.3</v>
+      <c r="X35" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3373,13 +3448,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="12" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>1.8</v>
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>7.3</v>
+        <v>23.2</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>10.8</v>
@@ -3397,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>16.5</v>
@@ -3414,33 +3489,31 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="12" t="n">
+      <c r="R36" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>26.4</v>
+        <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17</v>
+        <v>1.3</v>
       </c>
       <c r="V36" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="12" t="n">
+      <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y36" s="12" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z36" s="12" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="X36" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3454,72 +3527,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D37" s="10" t="n">
-        <v>1138.8</v>
+        <v>130.8</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>88.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>49.9</v>
+      <c r="G37" s="3" t="n">
+        <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>898</v>
+        <v>87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>210.9</v>
+        <v>40.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L37" s="12" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>82.59999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>82.2</v>
+        <v>89.5</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>12.6</v>
+        <v>420.9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44.5</v>
+        <v>149.4</v>
       </c>
       <c r="Q37" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="R37" s="12" t="n">
-        <v>102.2</v>
+      <c r="R37" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>208.6</v>
+        <v>120.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="V37" s="12" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V37" s="10" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="10" t="n">
-        <v>18.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>156</v>
+        <v>12.8</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3547,8 +3622,8 @@
       <c r="F38" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>92.09999999999999</v>
+      <c r="G38" s="12" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>17</v>
@@ -3557,54 +3632,54 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="12" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="O38" s="12" t="n">
+      <c r="M38" s="10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="P38" s="12" t="n">
+      <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Q38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="12" t="n">
+      <c r="R38" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>57.7</v>
+        <v>5.4</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="10" t="n">
-        <v>240.1</v>
-      </c>
-      <c r="W38" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.3</v>
+      <c r="V38" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="W38" s="10" t="n">
+        <v>12790.1</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>111.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3618,72 +3693,76 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E39" s="12" t="n">
+      <c r="C39" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>8</v>
+      <c r="F39" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L39" s="12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>8.4</v>
+        <v>84.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="14" t="inlineStr"/>
-      <c r="S39" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="R39" s="9" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V39" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W39" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v>75.42999999999999</v>
+      </c>
+      <c r="W39" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+        <v>64.8</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>48.8</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3697,66 +3776,66 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>22.8</v>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.4</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.4</v>
+        <v>16.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="8" t="n">
-        <v>8</v>
+      <c r="J40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>88.3</v>
+        <v>84</v>
       </c>
       <c r="P40" s="12" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="12" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>18.6</v>
+      <c r="W40" s="12" t="n">
+        <v>18.2</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>20.1</v>
@@ -3779,25 +3858,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>22.1</v>
+        <v>11.1</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
+        <v>20.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3805,49 +3884,49 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>1.7</v>
+      <c r="M41" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W41" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3862,70 +3941,74 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
-        <v>30.4</v>
+      <c r="D42" s="9" t="n">
+        <v>48.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>14</v>
+      <c r="F42" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N42" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="O42" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="P42" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R42" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="O42" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R42" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="n">
+      <c r="S42" s="12" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T42" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>57</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3942,17 +4025,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="8" t="n">
-        <v>18.5</v>
+        <v>20.4</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>19.2</v>
+        <v>174.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3963,50 +4048,50 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="L43" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>18.8</v>
+      <c r="R43" s="9" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>26.9</v>
       </c>
       <c r="W43" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X43" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y43" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z43" s="12" t="n">
+      <c r="Y43" s="3" t="n">
         <v>14.8</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4022,51 +4107,51 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>98</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>21.7</v>
+        <v>1.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>14.2</v>
+        <v>26.1</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>15.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>1.5</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
+        <v>154.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4075,12 +4160,14 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="n">
+      <c r="U44" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="3" t="n">
-        <v>30</v>
+      <c r="W44" s="12" t="n">
+        <v>20.6</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4088,7 +4175,9 @@
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4104,70 +4193,74 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>1.8</v>
+        <v>11.6</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>22.1</v>
+        <v>8504.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>830.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>28.1</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>15.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61</v>
+        <v>53.5</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>9.9</v>
+        <v>61.3</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>1089.6</v>
+        <v>59.4</v>
       </c>
       <c r="M45" s="10" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="N45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="n">
+        <v>12499</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>650.2</v>
+        <v>11651.1</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>1.3</v>
+        <v>1181.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>746.4</v>
+        <v>1113.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>217.9</v>
+        <v>517.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>107.1</v>
+        <v>187.1</v>
       </c>
       <c r="V45" s="10" t="n">
-        <v>12.8</v>
+        <v>145.1</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>114.8</v>
+        <v>111.6</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.8</v>
+        <v>392.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>1156.4</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4182,17 +4275,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="9" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="12" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>22.8</v>
+      <c r="F46" s="12" t="n">
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4203,20 +4296,22 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>98.8</v>
+      </c>
       <c r="L46" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M46" s="10" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="O46" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N46" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O46" s="12" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="P46" s="3" t="n">
+      <c r="P46" s="12" t="n">
         <v>3.6</v>
       </c>
       <c r="Q46" s="10" t="n">
@@ -4225,28 +4320,30 @@
       <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>19.3</v>
+      <c r="S46" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
